--- a/delivrables/annex/2.1/Capabilities - Responses.xlsx
+++ b/delivrables/annex/2.1/Capabilities - Responses.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/FabioCruz/Documents/01-Projects/TechTraPlastiCE/techtraplastice/delivrables/annex/2.1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B874DF0-B926-1F46-976A-BE115F7DAF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D89EF5-85D8-A844-8758-658081D1497A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Table_1[[#All],[Universidad]:[Palabras clave de la capacidad]]</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -3513,6 +3516,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -3524,6 +3528,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3578,16 +3583,6 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial (Corps)"/>
-      </font>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3630,6 +3625,16 @@
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial (Corps)"/>
+      </font>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3676,20 +3681,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:L79" headerRowDxfId="0" dataDxfId="1" totalsRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:L79" headerRowDxfId="14" dataDxfId="13" totalsRowDxfId="12">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Universidad" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Título corto en ESPAÑOL" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Título corto en INGLÉS" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Subtítulo en ESPAÑOL" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Subtítulo en INGLÉS" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Descripción en ESPAÑOL" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Descripción en INGLÉS" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Aplicaciones en ESPAÑOL" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Aplicaciones en INGLÉS" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Foto representativa de la capacidad" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Palabras clave de la capacidad" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Contacto" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Universidad" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Título corto en ESPAÑOL" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Título corto en INGLÉS" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Subtítulo en ESPAÑOL" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Subtítulo en INGLÉS" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Descripción en ESPAÑOL" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Descripción en INGLÉS" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Aplicaciones en ESPAÑOL" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Aplicaciones en INGLÉS" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Foto representativa de la capacidad" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Palabras clave de la capacidad" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Contacto" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Respuestas de formulario 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3909,9 +3914,9 @@
     <col min="7" max="7" width="73.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="47.6640625" style="2" customWidth="1"/>
     <col min="9" max="9" width="44" style="2" customWidth="1"/>
-    <col min="10" max="10" width="31.1640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="31.1640625" style="2" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="19.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" style="2" hidden="1" customWidth="1"/>
     <col min="13" max="16384" width="12.6640625" style="2"/>
   </cols>
   <sheetData>
@@ -7915,7 +7920,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="35" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
+  <pageSetup paperSize="9" scale="28" fitToWidth="2" fitToHeight="5" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
   <tableParts count="1">
     <tablePart r:id="rId78"/>
   </tableParts>
